--- a/artfynd/A 32986-2025 artfynd.xlsx
+++ b/artfynd/A 32986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>95684424</v>
+        <v>95684376</v>
       </c>
       <c r="B2" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>410716.633053383</v>
+        <v>410887</v>
       </c>
       <c r="R2" t="n">
-        <v>6706832.67666366</v>
+        <v>6706893</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,15 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>95684504</v>
+        <v>95684485</v>
       </c>
       <c r="B3" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78993</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -803,34 +783,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>353</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gärsjön, Öst, Vrm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>410911.8094477316</v>
+        <v>410988</v>
       </c>
       <c r="R3" t="n">
-        <v>6706957.042699385</v>
+        <v>6706963</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,27 +843,18 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,50 +873,48 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>95684514</v>
+        <v>95684484</v>
       </c>
       <c r="B4" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92083</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>1503</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Miettinen</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Gärsjön, Öst, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>410907.7481280228</v>
+        <v>410988</v>
       </c>
       <c r="R4" t="n">
-        <v>6707052.791195822</v>
+        <v>6706963</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,27 +944,18 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1011,15 +974,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>95684485</v>
+        <v>95684377</v>
       </c>
       <c r="B5" t="n">
-        <v>77177</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1027,37 +985,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Gärsjön, Öst, Vrm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>410988.0096627311</v>
+        <v>410704</v>
       </c>
       <c r="R5" t="n">
-        <v>6706963.055143383</v>
+        <v>6706771</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1087,28 +1042,17 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1127,53 +1071,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>95684484</v>
+        <v>95684378</v>
       </c>
       <c r="B6" t="n">
-        <v>89545</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93209</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1503</v>
+        <v>4366</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Skarp dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Hydnellum peckii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
+          <t>Banker</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Gärsjön, Öst, Vrm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>410988.0096627311</v>
+        <v>410925</v>
       </c>
       <c r="R6" t="n">
-        <v>6706963.055143383</v>
+        <v>6707058</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1203,28 +1139,17 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1243,37 +1168,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>95684378</v>
+        <v>95684375</v>
       </c>
       <c r="B7" t="n">
-        <v>90665</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4366</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skarp dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Hydnellum peckii</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Banker</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1203,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>410924.6738956895</v>
+        <v>410887</v>
       </c>
       <c r="R7" t="n">
-        <v>6707058.29059817</v>
+        <v>6706893</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1316,19 +1236,9 @@
           <t>2021-08-18</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2021-08-18</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,6 +1262,1170 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>95684424</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>410716</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6706833</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>95684503</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>410716</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6706880</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>95684507</v>
+      </c>
+      <c r="B10" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>410714</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6706781</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>95684374</v>
+      </c>
+      <c r="B11" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>410924</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6707101</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>95684384</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79084</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6446</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Carbonicola anthracophila</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>410895</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6706896</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>95684373</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>410924</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6707101</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>95684385</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>410895</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6706896</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>95684447</v>
+      </c>
+      <c r="B15" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>410923</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6707105</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>95684450</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>410906</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6706887</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>95684504</v>
+      </c>
+      <c r="B17" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>410912</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6706957</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>95684513</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>410997</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6706966</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>95684514</v>
+      </c>
+      <c r="B19" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Gärsjön, Öst, Vrm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>410908</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6707053</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Torsby</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Norra Ny</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2021-08-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Helena Malmestrand, Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32986-2025 artfynd.xlsx
+++ b/artfynd/A 32986-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684377</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684424</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684503</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684507</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684376</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1258,6 +1288,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684485</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1359,6 +1394,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684484</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1456,6 +1496,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684378</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1553,6 +1598,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684375</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1650,6 +1700,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684374</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1747,6 +1802,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684384</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1844,6 +1904,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684373</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1941,6 +2006,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684385</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2038,6 +2108,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684447</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2135,6 +2210,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684450</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2232,6 +2312,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684504</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2329,6 +2414,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684513</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2426,8 +2516,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/95684514</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>